--- a/backend/inventory.xlsx
+++ b/backend/inventory.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,35 +476,40 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>online_price</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>min_stock</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>supplier</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
@@ -513,7 +518,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33330c8e-bb82-4810-96c8-7e4034c6ff55</t>
+          <t>3ae852d5-675a-4386-bf54-c65e14662438</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -521,8 +526,10 @@
           <t>MTC-300</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>899100300001</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>899100300001</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -561,39 +568,42 @@
         <v>6500000</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>6800000</v>
       </c>
       <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
         <v>3</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Rak A-01</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>PT Sumber Teknik</t>
         </is>
       </c>
-      <c r="P2" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-08-19T04:06:03.375337+00:00</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-19T04:07:25.672594+00:00</t>
+          <t>2026-09-04T07:08:55.442415+00:00</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-09-04T07:08:55.442424+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1698e1e9-208e-4c56-8acb-103c485eed52</t>
+          <t>8f492cb0-efbf-44ac-8fec-4ccc1ce23a93</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -601,8 +611,10 @@
           <t>KTN-87A05</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>899100300002</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>899100300002</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -641,39 +653,42 @@
         <v>3200000</v>
       </c>
       <c r="L3" t="n">
+        <v>3350000</v>
+      </c>
+      <c r="M3" t="n">
         <v>13</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Rak B-02</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>KING TONY Indonesia</t>
         </is>
       </c>
-      <c r="P3" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-08-19T04:06:03.375353+00:00</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-19T04:06:03.375355+00:00</t>
+          <t>2026-09-04T07:08:55.442431+00:00</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-09-04T07:08:55.442433+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>372fdc3d-87f2-4784-94a0-556e7040eb90</t>
+          <t>f6129e76-597e-4b92-81d6-d6c57f005c65</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -681,8 +696,10 @@
           <t>INS-2301-10</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>899100300003</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>899100300003</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -721,32 +738,35 @@
         <v>1100000</v>
       </c>
       <c r="L4" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="M4" t="n">
         <v>20</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>5</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Rak C-01</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>INSIZE Official</t>
         </is>
       </c>
-      <c r="P4" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-08-19T04:06:03.375359+00:00</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-19T04:06:03.375361+00:00</t>
+          <t>2026-09-04T07:08:55.442438+00:00</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-09-04T07:08:55.442439+00:00</t>
         </is>
       </c>
     </row>
@@ -761,7 +781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,7 +854,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>caf0c1dc-31a0-4b90-b621-22a7e4a1c9f5</t>
+          <t>e9501658-d9c5-4678-89e7-5a5a4a7ce2db</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -884,14 +904,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-19T04:06:03.375370+00:00</t>
+          <t>2026-09-04T07:08:55.442449+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ede5b779-7496-4dd0-9f7a-b433961c2d38</t>
+          <t>eb93f99d-1f92-4104-8b76-97127bedb3d8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -941,14 +961,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-19T04:06:03.375376+00:00</t>
+          <t>2026-09-04T07:08:55.442455+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>098b3fe6-c9f9-4c29-9133-74811da143b8</t>
+          <t>f8fb2584-195c-4353-8ef5-007ccbf2d762</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -998,14 +1018,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-19T04:06:03.375381+00:00</t>
+          <t>2026-09-04T07:08:55.442459+00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4cf1ab49-3ece-4b38-ad1e-4b7bdc075756</t>
+          <t>b8879f96-4e27-4517-9370-fd87a0d1b97b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1055,227 +1075,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>76d4689a-0002-4e19-b8b6-061982b1df63</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GR-TEST-001</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MTC-300</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Tire Charger</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Barang Masuk</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Uji alur</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-08-19T04:06:27.569645+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>af54954c-2c60-4480-82e0-07393db51883</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>INV-TEST-001</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MTC-300</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tire Charger</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Penjualan</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Uji alur</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-08-19T04:06:27.706332+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>74dbd341-0f46-4ffb-ac28-3beb28fa6b49</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TEST-59c454b1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MTC-300</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Tire Charger</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Barang Masuk</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>13</v>
-      </c>
-      <c r="I8" t="n">
-        <v>14</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-08-19T04:07:25.582215+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>c9ca4e4d-12d2-4efe-b13c-cce0129f0e0a</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TEST-f116497d</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MTC-300</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Tire Charger</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Penjualan</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>14</v>
-      </c>
-      <c r="I9" t="n">
-        <v>13</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-08-19T04:07:25.672594+00:00</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,15 +1156,20 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>payment_status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>payment_method</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1373,7 +1178,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4fd3ccd3-6aca-48d6-be30-93be2d9e34ad</t>
+          <t>5a61844e-2adb-4df7-9e1e-35f24a111e85</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1383,7 +1188,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1423,141 +1228,20 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>fc027afb-943d-4e3d-af52-9544cd9f1ef2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>INV-TEST-001</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CV Uji Coba</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MTC-300</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tire Charger</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Selesai</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Transfer</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Uji alur</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>da91d5b6-c367-407c-8c45-74a311668cc4</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TEST-f116497d</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MTC-300</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tire Charger</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Selesai</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Transfer</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/inventory.xlsx
+++ b/backend/inventory.xlsx
@@ -526,10 +526,8 @@
           <t>MTC-300</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>899100300001</t>
-        </is>
+      <c r="C2" t="n">
+        <v>899100300001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -571,7 +569,7 @@
         <v>6800000</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -596,7 +594,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-04T07:08:55.442424+00:00</t>
+          <t>2026-09-04T07:14:20.249676+00:00</t>
         </is>
       </c>
     </row>
@@ -611,10 +609,8 @@
           <t>KTN-87A05</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>899100300002</t>
-        </is>
+      <c r="C3" t="n">
+        <v>899100300002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -696,10 +692,8 @@
           <t>INS-2301-10</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>899100300003</t>
-        </is>
+      <c r="C4" t="n">
+        <v>899100300003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -781,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,6 +1070,120 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1de3f46f-963e-454d-a663-8b4db37bd86b</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GR-960473</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Barang Masuk</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>on stocl</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-04T07:14:19.384855+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>18ce311c-f924-4d8f-add0-fa12ed7e08fc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GR-960473</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Barang Masuk</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>on stocl</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-04T07:14:20.249676+00:00</t>
         </is>
       </c>
     </row>

--- a/backend/inventory.xlsx
+++ b/backend/inventory.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:20.249676+00:00</t>
+          <t>2026-09-07T08:27:45.652667+00:00</t>
         </is>
       </c>
     </row>

--- a/backend/inventory.xlsx
+++ b/backend/inventory.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,7 +569,7 @@
         <v>6800000</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -594,7 +594,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-07T08:27:45.652667+00:00</t>
+          <t>2026-09-22T09:18:32.779505+00:00</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>3350000</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
         <v>5</v>
@@ -677,90 +677,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-09-04T07:08:55.442433+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>f6129e76-597e-4b92-81d6-d6c57f005c65</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>INS-2301-10</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>899100300003</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Dial Indicator INSIZE 2301-10</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Dial Indicator</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Measuring Tools</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>INSIZE</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2301-10</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>750000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Rak C-01</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>INSIZE Official</t>
-        </is>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-09-04T07:08:55.442438+00:00</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026-09-04T07:08:55.442439+00:00</t>
+          <t>2026-09-22T09:18:22.377671+00:00</t>
         </is>
       </c>
     </row>
@@ -775,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,6 +1101,165 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>2026-09-04T07:14:20.249676+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>42dd2bcc-86a0-477e-96f3-a11bc348e970</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INV-TEST-CICIL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:18:10.692634+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>af354039-afd6-4171-8c5e-ed62750236c0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INV-TEST-TEMPO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>KTN-87A05</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tool Box Set KING TONY 85PCS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>13</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:18:22.377671+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>44716e0b-6501-450a-9094-aa866ca48915</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INV-TEST-LATE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:18:32.779505+00:00</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,6 +1358,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>due_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1350,6 +1431,226 @@
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>46aac522-64dc-4a48-ac91-07224b14e4ad</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INV-TEST-CICIL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CV B</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>f493f5d5-bb27-4dd2-b537-9eeeb7120c83</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INV-TEST-TEMPO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Toko A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KTN-87A05</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tool Box Set KING TONY 85PCS</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>a4a1e395-5720-4d71-ae3c-be3481af973b</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INV-TEST-LATE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PT Lambat</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Cicilan</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/inventory.xlsx
+++ b/backend/inventory.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,10 +549,8 @@
           <t>MTC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="H2" t="n">
+        <v>300</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -569,7 +567,7 @@
         <v>6800000</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -594,90 +592,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-22T09:18:32.779505+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>8f492cb0-efbf-44ac-8fec-4ccc1ce23a93</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>KTN-87A05</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>899100300002</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Tool Box Set KING TONY 85PCS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Tool Box Set</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Hand Tools</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>KING TONY</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>87A05</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3350000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>12</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Rak B-02</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>KING TONY Indonesia</t>
-        </is>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-09-04T07:08:55.442431+00:00</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-09-22T09:18:22.377671+00:00</t>
+          <t>2026-09-22T09:21:58.580115+00:00</t>
         </is>
       </c>
     </row>
@@ -692,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1260,6 +1175,271 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>2026-09-22T09:18:32.779505+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2b413933-c42e-4500-8eec-c9a720e116f3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INV-20260922-001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:20:20.067482+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>c6c4cc3f-1dad-4e18-8e6b-fecb00e8ecef</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>INV-20260922-002</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:20:20.098649+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>c78c163c-9abb-46b3-b9ec-837c6d74ffa8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>INV-20260922-003</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:20:20.223756+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>d697f42d-7b26-4d61-b383-52750feaf878</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>INV-20260922-004</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:20:49.202096+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3bd505fb-b235-43b9-871c-abed7406a186</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>INV-20260922-005</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Penjualan</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:21:58.580115+00:00</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1632,7 +1812,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Cicilan</t>
+          <t>Lunas</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1649,6 +1829,367 @@
       <c r="Q5" t="inlineStr">
         <is>
           <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>9eedf1e5-f4e5-4bcd-86ec-e59e725268ad</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INV-20260922-001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TEST_TempoOK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>83e7fd88-42d2-4c04-9d6f-ed663b38d554</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INV-20260922-002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TEST_MarkPaid</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>740734f9-174d-4da8-a518-49727ec05ac7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INV-20260922-003</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TEST_Lunas</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Lunas</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>c3b2bbe4-6273-4bf6-baf8-eb1b2b2dcdc5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INV-20260922-004</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>UI TEST TEMPO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>c6b90910-a1e2-4f77-9be8-1a860cc6429f</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INV-20260922-005</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>pak test</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MTC-300</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tire Charger</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Selesai</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Cicilan</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
